--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425632</v>
       </c>
       <c r="B2" t="n">
-        <v>82990</v>
+        <v>82994</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>129425638</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>129425629</v>
       </c>
       <c r="B4" t="n">
-        <v>80081</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425632</v>
       </c>
       <c r="B2" t="n">
-        <v>82994</v>
+        <v>82995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,32 +775,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129425638</v>
+        <v>129425629</v>
       </c>
       <c r="B3" t="n">
-        <v>92151</v>
+        <v>80084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1179</v>
+        <v>6457</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420029</v>
+        <v>420031</v>
       </c>
       <c r="R3" t="n">
-        <v>6661670</v>
+        <v>6661714</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,11 +849,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På klen lövlåga, troligen hägg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,32 +875,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129425629</v>
+        <v>129425638</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>92153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6457</v>
+        <v>1179</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420031</v>
+        <v>420029</v>
       </c>
       <c r="R4" t="n">
-        <v>6661714</v>
+        <v>6661670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,6 +949,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På klen lövlåga, troligen hägg.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -775,32 +775,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129425629</v>
+        <v>129425638</v>
       </c>
       <c r="B3" t="n">
-        <v>80084</v>
+        <v>92157</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6457</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420031</v>
+        <v>420029</v>
       </c>
       <c r="R3" t="n">
-        <v>6661714</v>
+        <v>6661670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,6 +849,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På klen lövlåga, troligen hägg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,32 +880,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129425638</v>
+        <v>129425629</v>
       </c>
       <c r="B4" t="n">
-        <v>92153</v>
+        <v>80084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1179</v>
+        <v>6457</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420029</v>
+        <v>420031</v>
       </c>
       <c r="R4" t="n">
-        <v>6661670</v>
+        <v>6661714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,11 +954,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På klen lövlåga, troligen hägg.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -778,7 +778,7 @@
         <v>129425638</v>
       </c>
       <c r="B3" t="n">
-        <v>92157</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -775,32 +775,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129425638</v>
+        <v>129425629</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>80084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1179</v>
+        <v>6457</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420029</v>
+        <v>420031</v>
       </c>
       <c r="R3" t="n">
-        <v>6661670</v>
+        <v>6661714</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,11 +849,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På klen lövlåga, troligen hägg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,32 +875,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129425629</v>
+        <v>129425638</v>
       </c>
       <c r="B4" t="n">
-        <v>80084</v>
+        <v>92161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6457</v>
+        <v>1179</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420031</v>
+        <v>420029</v>
       </c>
       <c r="R4" t="n">
-        <v>6661714</v>
+        <v>6661670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,6 +949,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På klen lövlåga, troligen hägg.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -775,32 +775,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129425629</v>
+        <v>129425638</v>
       </c>
       <c r="B3" t="n">
-        <v>80084</v>
+        <v>92161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6457</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420031</v>
+        <v>420029</v>
       </c>
       <c r="R3" t="n">
-        <v>6661714</v>
+        <v>6661670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,6 +849,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På klen lövlåga, troligen hägg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,32 +880,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129425638</v>
+        <v>129425629</v>
       </c>
       <c r="B4" t="n">
-        <v>92161</v>
+        <v>80084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1179</v>
+        <v>6457</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420029</v>
+        <v>420031</v>
       </c>
       <c r="R4" t="n">
-        <v>6661670</v>
+        <v>6661714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,11 +954,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På klen lövlåga, troligen hägg.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425632</v>
       </c>
       <c r="B2" t="n">
-        <v>82995</v>
+        <v>83022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>129425638</v>
       </c>
       <c r="B3" t="n">
-        <v>92161</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>129425629</v>
       </c>
       <c r="B4" t="n">
-        <v>80084</v>
+        <v>80110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425632</v>
       </c>
       <c r="B2" t="n">
-        <v>83022</v>
+        <v>83027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>129425638</v>
       </c>
       <c r="B3" t="n">
-        <v>92189</v>
+        <v>92195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>129425629</v>
       </c>
       <c r="B4" t="n">
-        <v>80110</v>
+        <v>80115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425632</v>
       </c>
       <c r="B2" t="n">
-        <v>83027</v>
+        <v>83028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>129425638</v>
       </c>
       <c r="B3" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>129425629</v>
       </c>
       <c r="B4" t="n">
-        <v>80115</v>
+        <v>80116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425632</v>
       </c>
       <c r="B2" t="n">
-        <v>83028</v>
+        <v>83033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>129425638</v>
       </c>
       <c r="B3" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>129425629</v>
       </c>
       <c r="B4" t="n">
-        <v>80116</v>
+        <v>80121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -778,7 +778,7 @@
         <v>129425638</v>
       </c>
       <c r="B3" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425632</v>
       </c>
       <c r="B2" t="n">
-        <v>83033</v>
+        <v>83035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>129425638</v>
       </c>
       <c r="B3" t="n">
-        <v>92205</v>
+        <v>92207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -775,32 +775,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129425638</v>
+        <v>129425629</v>
       </c>
       <c r="B3" t="n">
-        <v>92207</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1179</v>
+        <v>6457</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420029</v>
+        <v>420031</v>
       </c>
       <c r="R3" t="n">
-        <v>6661670</v>
+        <v>6661714</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,11 +849,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På klen lövlåga, troligen hägg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,32 +875,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129425629</v>
+        <v>129425638</v>
       </c>
       <c r="B4" t="n">
-        <v>80121</v>
+        <v>92207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6457</v>
+        <v>1179</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420031</v>
+        <v>420029</v>
       </c>
       <c r="R4" t="n">
-        <v>6661714</v>
+        <v>6661670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,6 +949,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På klen lövlåga, troligen hägg.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -878,7 +878,7 @@
         <v>129425638</v>
       </c>
       <c r="B4" t="n">
-        <v>92531</v>
+        <v>92533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129425632</v>
+        <v>129425638</v>
       </c>
       <c r="B2" t="n">
-        <v>83035</v>
+        <v>92559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>1179</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420034</v>
+        <v>420029</v>
       </c>
       <c r="R2" t="n">
-        <v>6661668</v>
+        <v>6661670</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,21 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På klen lövlåga, troligen hägg. Kollad med mikroskop av Moa Björnberg Dillner. Sporernas mått stämmer, skeletthyferna färgas rödbruna i melzers.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -775,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129425629</v>
+        <v>129425632</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>83290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -786,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6457</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -813,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420031</v>
+        <v>420034</v>
       </c>
       <c r="R3" t="n">
-        <v>6661714</v>
+        <v>6661668</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,32 +885,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129425638</v>
+        <v>129425629</v>
       </c>
       <c r="B4" t="n">
-        <v>92533</v>
+        <v>80367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1179</v>
+        <v>6457</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420029</v>
+        <v>420031</v>
       </c>
       <c r="R4" t="n">
-        <v>6661670</v>
+        <v>6661714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,21 +961,11 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På klen lövlåga, troligen hägg. Kollad med mikroskop av Moa Björnberg Dillner. Sporernas mått stämmer, skeletthyferna färgas rödbruna i melzers.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG4" t="b">
         <v>0</v>

--- a/artfynd/A 72412-2021 artfynd.xlsx
+++ b/artfynd/A 72412-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425638</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425632</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,8 +997,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>